--- a/politicians/matteosalvinimi_tweets.xlsx
+++ b/politicians/matteosalvinimi_tweets.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t>“La guerra finirà, non posso dire quando, ma finirà. Sono fiducioso che la risolveremo” - Donald J. Trump, 18 agosto 2025. E noi speriamo che nessuno, a Bruxelles o a Parigi, si metta di traverso sulla via della Pace.</t>
   </si>
@@ -176,12 +176,504 @@
   <si>
     <t>Shanghai Yangshan, in Cina, il più grande porto del mondo: 50 milioni di container l’anno, tutto automatizzato e all’avanguardia. Vent’anni fa c’era solo mare, oggi c’è un modello di sviluppo, tecnologia e lavoro. Sto visitando porti, aziende e cantieri per portare in Italia più innovazione, più occupazione, più futuro. Stiamo lavorando su tutti i porti italiani per renderli più moderni, più veloci, più competitivi. Perché ogni container è ricchezza e lavoro per il nostro Paese. L’Italia deve continuare a correre.</t>
   </si>
+  <si>
+    <t>Lavoro e crescita. Vogliamo creare spazio per le imprese italiane all’estero, anche in Cina e Giappone. Più investimenti, più occupazione, più futuro. L’Italia può e deve essere sempre più protagonista nel mondo.</t>
+  </si>
+  <si>
+    <t>Pechino, questa mattina incontro istituzionale con il Ministro dei Trasporti cinese, Liu Wei. Un confronto costruttivo sulle rispettive strategie infrastrutturali: dall’alta velocità ferroviaria alla mobilità sostenibile, passando per le grandi opere come il Ponte sullo Stretto, che ha destato grande interesse. Un’occasione importante per rafforzare il dialogo e per promuovere il nostro Paese.</t>
+  </si>
+  <si>
+    <t>Questa mattina affascinante sopralluogo sul ponte di Akashi, in Giappone, tra i più lunghi del mondo tra quelli a campata unica. Un'opera che ha cambiato in meglio la vita delle comunità. Adesso tocca a noi: il Ponte sullo Stretto sarà ancora più imponente, con torri da 399 metri, sei corsie stradali, due binari ferroviari, nessun pilone in acqua per una lunghezza superiore ai 3 chilometri. Lo fanno in Giappone, in Cina, in Scandinavia, negli Stati Uniti... adesso, dopo anni di attesa, finalmente siamo pronti a partire anche in Italia. Facendolo meglio.</t>
+  </si>
+  <si>
+    <t>Oggi a Tokyo, ospite del Ministro dei Trasporti Hiromasa Nakano, per la firma del Memorandum di Collaborazione sulla costruzione di ponti a campata unica, quindi a Osaka, per fare visita a Expo 2025, un evento straordinario e una vetrina senza pari per il nostro Paese. Il padiglione italiano è il più visitato di tutta la manifestazione. Milioni di visitatori da tutto il mondo per conoscere e ammirare le nostre eccellenze. Grande orgoglio italiano.</t>
+  </si>
+  <si>
+    <t>Non solo una grande amicizia, quella tra Italia e Giappone, ma anche una collaborazione concreta, per garantire più investimenti, più opportunità, più lavoro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buongiorno da Tokyo. Questa mattina al Ministero delle Infrastrutture e dei Trasporti del Giappone ho incontrato il collega ministro @Hiro_NAKANO_, per la firma del Memorandum di Collaborazione sulla costruzione, gestione e manutenzione di ponti a campata unica.
+Un utile confronto, una condivisione di esperienze e sfide comuni sul fronte delle infrastrutture, alla vigilia della visita che farò domani al Ponte dello stretto di Akashi, “gemello” di quello progettato per lo stretto di Messina e il secondo ponte sospeso più lungo al mondo.
+Italia e Giappone, due Paesi e due popoli amici, che collaborano insieme per garantire crescita, sviluppo, lavoro. </t>
+  </si>
+  <si>
+    <t>Intensa giornata di lavoro a Tokyo: incontri con i vertici di Toyota, Honda e con il Presidente della Camera giapponese, per rafforzare i rapporti industriali e commerciali tra Italia e Giappone. Più investimenti in Italia significa più lavoro per operai, tecnici e giovani italiani. E stop alle ideologie green che penalizzano il settore industriale dell'auto e della moto italiano e occidentale: servono pragmatismo, collaborazione e visione per il futuro. Avanti tutta, con al centro il lavoro! Vi tengo aggiornati.</t>
+  </si>
+  <si>
+    <t>Grazie a Fukushiro Nukaga, presidente della Camera dei Rappresentanti del Giappone, che ho incontrato oggi a Tokyo. È stata un’occasione importante per ribadire l’amicizia tra i nostri due Paesi e auspicare una sempre maggiore cooperazione.</t>
+  </si>
+  <si>
+    <t>Buongiorno dal Giappone. Questa mattina a Tokyo, alla presenza dell’ambasciatore italiano Gianluigi Benedetti, ho incontrato i vertici di Toyota e Honda, due importanti e storici marchi nipponici dell’automotive da tempo radicati in Italia. Dialoghi concreti e costruttivi, tanti spunti di discussione. Ho condiviso con loro tutte le perplessità sul Green Deal Ue e i rischi legati al “tutto elettrico” e ribadito l’impegno a difendere il settore in maniera concreta.</t>
+  </si>
+  <si>
+    <t>Vittoria della signora Margherita che non ha mai mollato, dei cittadini di Vicenza che l’hanno sostenuta, del ministro Piantedosi e della Lega, che sui temi della sicurezza e del contrasto all’immigrazione irregolare non cede di un millimetro.</t>
+  </si>
+  <si>
+    <t>Un’esplosione impressionante nel quartiere Prenestino, a Roma, ha provocato decine di feriti. Esprimo vicinanza, gratitudine e solidarietà ai Vigili del Fuoco, alle Forze dell’Ordine, ai soccorritori. Stiamo seguendo la vicenda con la massima attenzione.</t>
+  </si>
+  <si>
+    <t>Uomo di Fede e di Pace. Per me grande gioia ed emozione.</t>
+  </si>
+  <si>
+    <t>Buon compleanno alla mia splendida mamma, che oggi spegne 79 candeline. Se sono quello che sono, è anche grazie a lei</t>
+  </si>
+  <si>
+    <t>Un piacere e un onore incontrare al MIT l'Ambasciatore degli Stati Uniti in Italia, @USAmbItaly.
+Un’occasione importante per ribadire lo storico legame di vicinanza e amicizia tra i nostri Paesi e per discutere di progetti infrastrutturali fondamentali per lo sviluppo nazionale. 
+Pronti a lavorare insieme</t>
+  </si>
+  <si>
+    <t>Dopo anni di proteste e di battaglie dei cittadini e della Lega, finalmente giustizia è fatta!</t>
+  </si>
+  <si>
+    <t>Promessa mantenuta: dopo 12 anni di lavori e 5 anni di chiusura, il Tunnel del Col di Tenda torna a unire Italia e Francia. Un’opera attesa da troppo tempo, che significa lavoro, commercio e turismo. Significa connessioni tra popoli, territori ed economie. Per qualcuno era impossibile: «Figurati se lo riaprono entro l’estate 2025…», dicevano. Noi lo abbiamo fatto. Grazie a operai, imprese, tecnici e alla pazienza di chi ha creduto in questo progetto. Costruire gallerie, strade e infrastrutture è il nostro modo di costruire pace e sviluppo. Avanti con concretezza, per l’Italia del futuro</t>
+  </si>
+  <si>
+    <t>In diretta da Limone Piemonte per la riapertura del tunnel del Tenda, chiuso da troppi anni. Finalmente si torna a collegare l’Italia con la Francia, un’opera fondamentale per i cittadini, per il lavoro e per il turismo. Avanti così!</t>
+  </si>
+  <si>
+    <t>Mi ha accusato di essere vicino alla criminalità organizzata, ma oggi non ha avuto il coraggio di andare fino in fondo. In tribunale si è nascosto dietro una citazione di Gaetano Salvemini e ha provato a buttarla in caciara parlando della sua scorta (che non gli è mai stata revocata). Roberto Saviano si è confermato un insultatore livoroso, alla disperata ricerca di visibilità.</t>
+  </si>
+  <si>
+    <t>Alla Camera per presentare i nuovi Dipartimenti Regionali Carceri e Polizia Penitenziaria. Il DL Sicurezza è un passo concreto. Serve riportare al centro l’impegno delle donne e degli uomini della Polizia Penitenziaria. Rispetto, attenzione, azione.</t>
+  </si>
+  <si>
+    <t>Quanti sorrisi ci hai regalato, col fischio o senza. RIP indimenticabile Pierino.</t>
+  </si>
+  <si>
+    <t>Un’ottima notizia: per la prima volta, niente ingresso a numero chiuso per la facoltà di Medicina. Una storica battaglia della Lega, diventata realtà. Dalle parole ai fatti!</t>
+  </si>
+  <si>
+    <t>GRAZIE a tutti i cittadini che questo fine settimana, da Nord a Sud, sono venuti ai mille gazebo dedicati al Decreto Sicurezza voluto dalla Lega. Una legge fondamentale su temi che per noi sono DA SEMPRE una priorità: per tutelare le Forze dell’ordine e difendere il più possibile la tranquillità degli italiani (legge che, chissà perché, non piace alla “democratica” sinistra. Pazienza!). P.s. Un grazie speciale a tutti i militanti e volontari della Lega che rendono possibile tutto questo</t>
+  </si>
+  <si>
+    <t>Mentre tanti giornali tacciono sulle motivazioni della mia assoluzione nel caso Open Arms, ecco un commento libero e obiettivo, con quella onestà intellettuale che dovrebbe essere condivisa da tutta la stampa, visto che sono stato a processo per anni rischiando pene gravissime semplicemente per aver fatto il mio dovere da Ministro dell’Interno.</t>
+  </si>
+  <si>
+    <t>Dal Santo Padre, parole importanti e di buonsenso per la PACE. Un messaggio che tutti dovrebbero ascoltare</t>
+  </si>
+  <si>
+    <t>I giudici hanno confermato che difendere l’Italia non è reato, rilevando l’ostinazione e l’arroganza di Open Arms che ha fatto di tutto per venire in Italia, scartando tutte le altre alternative che erano più logiche e naturali. La soddisfazione per la decisione dei giudici di Palermo non cancella l’amarezza per un processo lungo e che è costato migliaia di euro ai contribuenti italiani: è il risultato dell’odio politico della sinistra contro di me.</t>
+  </si>
+  <si>
+    <t>Solidarietà al grande Don Coluccia, prete coraggioso aggredito da criminali che temono il suo impegno anti-spaccio. Abbiamo il dovere di aiutarlo con leggi come il Decreto Sicurezza, e sono pronto ad accompagnarlo nel suo prossimo blitz per la legalità al Quarticciolo.</t>
+  </si>
+  <si>
+    <t>Inserire la frase – significativa e potente – di Paolo Borsellino tra le tracce degli esami di maturità è una scelta che condivido e approvo. Grazie al nostro ministro Valditara: da anni la lotta alla mafia era assente dalle tracce d’esame. Questo è un doveroso tributo alle idee e all’impegno di un eroe, valori che vanno trasmessi ai nostri giovani. La sua battaglia resta ancora oggi un esempio e una guida per tutti noi, ogni giorno.</t>
+  </si>
+  <si>
+    <t>A sei mesi dall’entrata in vigore del nuovo Codice della Strada, proseguono i dati positivi: meno morti, meno feriti, meno incidenti. Le misure adottate stanno dando risultati concreti, grazie al lavoro insostituibile e costante delle donne e degli uomini in divisa. Un trend incoraggiante, che conferma che la direzione è quella giusta.</t>
+  </si>
+  <si>
+    <t>Dopo tanti no e tante scelte ideologiche (e irrazionali) arrivano buonsenso e concretezza, grazie alla Lega - che sul tema del nucleare pulito e di ultima generazione ha da sempre le idee chiare - e all'impegno di tutto il governo. Per assicurare all'Italia e al suo sistema produttivo un futuro di autonomia ed efficienza energetica.</t>
+  </si>
+  <si>
+    <t>Auguri sorellina mia! Sono passati 45 anni da quando hai aperto gli occhi sul mondo, e il sorriso è sempre lo stesso.</t>
+  </si>
+  <si>
+    <t>In collegamento dal Ministero il mio intervento all’evento organizzato da Federchimica Assogasliquidi: “Il GNL e il BioGNL, soluzioni di oggi e di domani per la decarbonizzazione dei trasporti e dell'industria”.</t>
+  </si>
+  <si>
+    <t>Pace fiscale e taglio Irpef possono andare insieme. E c’è anche da aumentare la soglia della flat tax, oggi per scelta europea bloccata a 85 mila euro: se salisse anche a 100-150 mila euro aumenterebbe la possibilità di lavorare, fatturare, dichiarare, aumenterebbe l’incasso per lo Stato.</t>
+  </si>
+  <si>
+    <t>“Carlo nella quotidianità ha offerto la sua vita adempiendo al proprio dovere con generosità e amore”. Il toccante ultimo saluto a Carlo Legrottaglie, brigadiere capo barbaramente ucciso da malviventi nel suo ultimo giorno di lavoro. Un eroe, un servitore dello Stato, fedele alla propria divisa fino all’estremo sacrificio. Alla sua memoria, il rispetto e la riconoscenza di un Paese intero. E dato che la riconoscenza si dimostra con i fatti, faremo di tutto per evitare che in futuro donne e uomini in divisa finiscano a processo per aver difeso i cittadini. Indagare i poliziotti che hanno ucciso il killer del carabiniere Legrottaglie è uno schiaffo all’Italia perbene.</t>
+  </si>
+  <si>
+    <t>In diretta da Rapallo per intervenire al 58° Convegno dei Giovani Imprenditori di Confindustria. Parliamo di futuro, impresa, lavoro e Italia. Mi seguite?</t>
+  </si>
+  <si>
+    <t>Faremo di tutto per evitare il blocco degli Euro 5, che danneggerebbe milioni di italiani in tutto il Paese solo per fare contente Ursula e Greta. La Lega ha presentato un emendamento ad hoc al decreto infrastrutture. E a livello europeo continuiamo a credere che il Green deal andrebbe abolito, sta solo aumentando l’inquinamento a livello globale (con Cina e India che bruciano carbone e aumentano le emissioni) e chiudendo le fabbriche in Europa.</t>
+  </si>
+  <si>
+    <t>La cittadinanza va meritata, non ricevuta in regalo.</t>
+  </si>
+  <si>
+    <t>Ora in diretta da Palazzo Madama, il mio intervento al convegno sul Decreto Sicurezza voluto dalla Lega. Più regole, più controlli, più difesa per gli italiani. Avanti con coraggio!</t>
+  </si>
+  <si>
+    <t>Ora in collegamento da Palazzo Chigi il mio intervento al direttivo ALIS, mi seguite?</t>
+  </si>
+  <si>
+    <t>Coraggio, sacrificio, disciplina. Onore e grazie alle donne e agli uomini in divisa che difendono il nostro Paese. Buona Giornata alla Marina Militare Italiana</t>
+  </si>
+  <si>
+    <t>Grande rispetto per chi è andato a votare, enorme sconfitta per una sinistra che non ha più idee e credibilità e che non riesce a mobilitare neanche i propri elettori. In due anni e mezzo al governo del Paese abbiamo ottenuto il record di italiani al lavoro, disoccupazione ai minimi, crescita dei posti fissi e calo del precariato: alla sinistra lasciamo le chiacchiere, Lega e governo rispondono coi fatti, e gli Italiani col voto (e il non voto) di ieri e oggi lo hanno capito benissimo. Cittadinanza accelerata? Idea sbagliata e bocciata pure quella, servono semmai più controlli e più buon senso. E sulla clandestinità, continuare a ridurre sbarchi e aumentare espulsioni. Gli Italiani hanno scelto, evviva la Democrazia.</t>
+  </si>
+  <si>
+    <t>In diretta da Mormant-sur-Vernisson, in Francia: il mio intervento all’evento dei Patrioti. L'Europa dei popoli è possibile, con più libertà, più sovranità, più sicurezza. Noi ci siamo. Mi seguite?</t>
+  </si>
+  <si>
+    <t>5 ore e 28 minuti di scontro tra due grandi campioni. Una partita incredibile, a prescindere dal finale. Congratulazioni ad Alcaraz per il risultato, ma applausi anche per il nostro Sinner, combattente straordinario, con una mentalità vincente sempre e comunque, a testa alta anche nella sconfitta. Un esempio per i nostri giovani, un esempio per tutti. Siamo orgogliosi di te</t>
+  </si>
+  <si>
+    <t>A Fontainebleau (Francia), per il summit dei Patrioti. Al lavoro per un’Europa diversa da quella attuale, dei popoli e non dei burocrati, amica e non nemica delle imprese, che non investe per le armi ma si impegna per la PACE.</t>
+  </si>
+  <si>
+    <t>Quanto avvenuto in Colombia al candidato presidenziale del centrodestra Miguel Uribe, ferito gravemente alla testa da un colpo d’arma da fuoco durante un comizio elettorale, lascia sgomenti. È un attentato alla democrazia che va condannato con fermezza. La violenza non può fermare la democrazia. A lui e al popolo comombiano la nostra solidarietà e vicinanza.</t>
+  </si>
+  <si>
+    <t>Parole in diretta, chiare e sincere, da parte di un uomo che ama il calcio, lo sport e l’Italia. E la nostalgia di un mondo del pallone che non c’è più. Bravo Silvio Baldini, che ne pensate?</t>
+  </si>
+  <si>
+    <t>Questa mattina a Roma, al Villaggio Arma 2025, per rendere omaggio ai Carabinieri. Orgoglioso di aver approvato un Decreto Sicurezza che tutela le Forze dell’ordine, difende gli onesti e punisce i delinquenti a partire da chi occupa le case. Dalla parte delle donne e degli uomini in divisa che servono il nostro Paese, sempre!</t>
+  </si>
+  <si>
+    <t>La Lega si batte affinché la castrazione chimica per stupratori e pedofili sia legge anche in Italia. È un’opzione che per gravi reati sessuali esiste già, in forme diverse, in molti Paesi al mondo, dagli Stati Uniti alla Corea del Sud, e nella stessa Europa: in Regno Unito dove è in fase di sperimentazione, ma anche in Polonia, Germania, Danimarca, Svezia e Belgio, solo per citarne alcuni. Voi che ne pensate?</t>
+  </si>
+  <si>
+    <t>Questa mattina alla Camera dei Deputati per partecipare alla Conferenza interparlamentare OSCE sulla lotta alla criminalità organizzata, con delegazioni provenienti da 33 Paesi, presieduta dal deputato della Lega Eugenio Zoffili, presidente della Delegazione parlamentare italiana e Rappresentante speciale dell'Assemblea parlamentare OSCE. Mafie, traffico di droga e tratta di esseri umani non conoscono confini e urge tolleranza zero: per contrastarli servono cooperazione costante, scambio di dati e controlli capillari. La testimonianza italiana dell'agenzia dei beni confiscati alle mafie può rappresentare un modello da seguire a livello internazionale. Più che di fantomatici eserciti europei, c’è bisogno di condivisione di conoscenze e competenze. Concretezza, rigore, serietà.</t>
+  </si>
+  <si>
+    <t>Vigliacchi. Totale solidarietà a Don Coluccia, eroico difensore dei giovani, della legalità e della vita, che ogni giorno combatte droga e criminalità. Al suo fianco, sempre!</t>
+  </si>
+  <si>
+    <t>In collegamento da Lamezia Terme con Roma per partecipare all’evento organizzato da La Verità. Al centro del dibattito: infrastrutture, trasporti e il futuro del Paese. Ci siete?</t>
+  </si>
+  <si>
+    <t>Sono già passati nove anni senza di te. Ci manchi, amico mio. Ciao Gianluca, sempre con noi!</t>
+  </si>
+  <si>
+    <t>Questa mattina al Viminale con il Ministro Matteo Piantedosi, per la firma del protocollo d’intesa tra Vigili del Fuoco e Autostrade dello Stato, finalizzato a rafforzare la sicurezza in autostrada. Sicurezza, condivisione dei dati e innovazione tecnologica saranno al centro di una collaborazione che punta a gestire le emergenze lungo la rete autostradale in modo più rapido, coordinato ed efficace. Un passo in avanti importante, all’insegna dell’innovazione e della concretezza.</t>
+  </si>
+  <si>
+    <t>Nella notte tra il 3 e il 4 giugno 1989, la strage di Piazza Tienanmen. A 36 anni di distanza, il coraggio di chi si è alzato in piedi per chiedere pacificamente diritti e democrazia parla ancora al mondo. Viva la libertà. Sempre.</t>
+  </si>
+  <si>
+    <t>Questo pomeriggio intervistato da @Tommasocerno nel corso dell’evento “Il futuro è ancora verde?”, organizzato a Roma dal quotidiano Il Tempo. Un confronto sulle infrastrutture, sui trasporti e sulle sfide importanti che attendono il nostro Paese. Avanti con l’Italia dei Sì!</t>
+  </si>
+  <si>
+    <t>Buona Festa della Repubblica!</t>
+  </si>
+  <si>
+    <t>Oggi si celebra la Giornata Mondiale dei Genitori. Un pensiero a tutte le mamme e i papà che, con amore e dedizione, crescono, educano e proteggono, trasmettendo i valori del rispetto e della responsabilità. Dietro ogni bambino felice ci sono il cuore e l’impegno di chi, ogni giorno, si prende cura di lui: una mamma e un papà. GRAZIE a tutti i genitori, a cominciare dai miei</t>
+  </si>
+  <si>
+    <t>Minacce social anche contro il ministro Piantedosi e le sue figlie. Parole vili, vigliacche, ingiustificabili, che non vanno sottovalutate. Clima d’odio inaccettabile. Solidarietà all’amico Matteo e alla sua famiglia.</t>
+  </si>
+  <si>
+    <t>Ora in collegamento con Genova per il Festival del Lavoro 2025, mi seguite?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una brutta notizia. Ci lascia un grande imprenditore e grande uomo di sport. Una preghiera </t>
+  </si>
+  <si>
+    <t>Il mio saluto per l’edizione 2025 del CPAC Hungary! Patrioti uniti per un’Europa diversa, libera, sovrana e fondata sui valori della famiglia, dell’identità e del lavoro. Contro l’immigrazione clandestina, contro l’ideologia woke e green, per un'Europa dei popoli e non dei burocrati. L’era dei Patrioti è solo all’inizio. Insieme, possiamo farcela. Make Europe Great Again!</t>
+  </si>
+  <si>
+    <t>Ecco come il Ponte sullo Stretto cambierà in meglio i collegamenti tra Calabria e Sicilia e le vite di milioni di cittadini. Benefici concreti, con impatti positivi per studenti, lavoratori, turisti. Una grande opportunità, per tutto il Paese. Avanti con l’Italia del Sì!</t>
+  </si>
+  <si>
+    <t>Approvata la legge “Salva Animali”. Pene e sanzioni più dure per chi sfrutta, maltratta o - maledetti! - uccide i nostri amici a quattro zampe. Una battaglia storica, mia e della Lega, che con questa legge segna una svolta epocale, di civiltà e amore! Dalle parole ai fatti. P.s. Grazie anche a tutti voi per il costante sostegno su questo tema</t>
+  </si>
+  <si>
+    <t>Una vicenda terribile. Una preghiera per Martina e un abbraccio alla madre, che ha pienamente ragione a chiedere il carcere a vita per l'assassino. Nessuno sconto per questo criminale.</t>
+  </si>
+  <si>
+    <t>Grazie alle proposte della Lega nel Decreto Sicurezza finalmente CI SIAMO: chi occupa abusivamente una casa verrà sgomberato in 24 ore. La proprietà privata, frutto dei risparmi e dei sacrifici di una vita, è sacra! DALLE PAROLE AI FATTI!</t>
+  </si>
+  <si>
+    <t>Una delle mie prime richieste ai vertici di Ferrovie dello Stato era rendere possibile la connessione durante l’intera tratta dell’Alta velocità. Fs, in totale autonomia, ha scelto due soggetti, con cui sta sperimentando la copertura satellitare. Garantire una connessione stabile e veloce a chi viaggia è un nostro obiettivo, per rendere il Paese più moderno, competitivo e proiettato nel futuro.</t>
+  </si>
+  <si>
+    <t>Oggi a Trento per partecipare alla XX edizione del Festival dell’Economia. Un’occasione importante di confronto su tematiche di attualità nazionali e internazionali. Nel panel “Le infrastrutture del futuro”, intervistato da @MariaLatella, ho parlato delle tantissime azioni che, come MIT, stiamo portando avanti per modernizzare il sistema Paese e prepararlo alle sfide del domani. Prosegue il lavoro per un’Italia più efficiente, più competitiva, più connessa.</t>
+  </si>
+  <si>
+    <t>Sopralluogo al cantiere del tunnel sub-portuale di Genova, un’opera che la città attende da tempo, un intervento di ingegneria avanzata per migliorare i collegamenti urbani e l’accessibilità al porto. 150 operai al lavoro, parchi al posto del cemento, meno traffico, più verde e più lavoro. Genova sta vivendo un rinascimento strutturale, e lo sta facendo grazie ai genovesi. Avanti con l’Italia dei Sì!</t>
+  </si>
+  <si>
+    <t>Due anni senza Maria Giovanna. La tua intelligenza, il tuo anticonformismo e la tua serietà oggi servirebbero come mai in precedenza. Adesso, in mezzo a tanto piattume, sarebbero preziosi. Ci manchi, amica mia. Le tue idee vivono con noi.</t>
+  </si>
+  <si>
+    <t>Espulso. Bene così, uno in meno da mantenere in Italia.</t>
+  </si>
+  <si>
+    <t>Vi ripropongo la mia intervista di poco fa su Rai 1 a “Cinque Minuti”, con Bruno Vespa.
+Buona serata Amici</t>
+  </si>
+  <si>
+    <t>Sono assolutamente contrario a qualsiasi tipo di riarmo europeo, perché siamo un Paese libero e sovrano. Se si tratta di investire soldi per la sicurezza interna e per assumere Carabinieri, sì. Se si tratta di fare debito in Italia per andare a comprare i carri armati a Berlino, no.</t>
+  </si>
+  <si>
+    <t>Yaron Lischinsky e Sarah Milgrim, dipendenti dell'Ambasciata Israeliana di Washington. Una giovane coppia in procinto di sposarsi. Uccisi senza motivo nei pressi del museo ebraico. L'aggressore, Elias Rodriguez, faceva parte di un gruppo di estrema sinistra. Due vite spezzate dal terrore e dall'odio antisemita verso due innocenti. Una preghiera e vicinanza alle famiglie delle vittime.</t>
+  </si>
+  <si>
+    <t>Nessuna tolleranza per la criminalità: complimenti ai Carabinieri per la brillante operazione. L’Italia è orgogliosa delle donne e degli uomini in divisa.</t>
+  </si>
+  <si>
+    <t>Addio a Nino Benvenuti, leggenda del pugilato e simbolo dello sport italiano. Oro olimpico, campione del mondo, un esempio dentro e fuori dal ring. Ciao grande campione.</t>
+  </si>
+  <si>
+    <t>Via libera ai fondi per i Gran Premi di Formula 1 di Monza e Imola. Un intervento concreto che evidenzia l’attenzione del Governo verso questi appuntamenti, non solo come eventi sportivi di livello mondiale, ma anche come fondamentali volani economici e vetrine internazionali per la Lombardia e per l’Emilia-Romagna. Promessa mantenuta!</t>
+  </si>
+  <si>
+    <t>Approvato oggi dal Consiglio dei Ministri il decreto legge Infrastrutture, un provvedimento strategico per sbloccare i cantieri, semplificare i contratti pubblici e potenziare i trasporti. Un altro passo in avanti per l'Italia dei Sì!</t>
+  </si>
+  <si>
+    <t>Onore all’amico George Simion, che alle elezioni presidenziali in Romania - dove è stato votato dalla maggioranza dei rumeni in Italia - ha combattuto a testa alta fino all’ultimo, contro tutto e contro tutti, a seguito di un furto di democrazia senza precedenti.</t>
+  </si>
+  <si>
+    <t>Grande successo per gli amici di Chega, alleati della Lega in Europa, alle elezioni parlamentari in Portogallo: miglior risultato di sempre! La famiglia dei Patrioti per l’Europa è sempre più forte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vittoria STORICA del centrodestra a #Bolzano! Congratulazioni al nuovo sindaco Claudio Corrarati. Proposte concrete e buonsenso: avanti con il cambiamento!
+</t>
+  </si>
+  <si>
+    <t>Teppisti di sinistra ancora contro poliziotti e cittadini, stavolta a Milano. Mentre la Lega assegna più potere e mezzi alle Forze dell’ordine, il PD spesso legalizza centri sociali e tace sulla violenza.</t>
+  </si>
+  <si>
+    <t>A cinque mesi dall’entrata in vigore del nuovo Codice della Strada, i dati certificano meno incidenti, meno feriti, meno vittime. Rispetto allo stesso periodo dell’anno scorso, 47 morti in meno sulle strade italiane, oltre 1.300 incidenti in meno e un calo generale su tutti i fronti, dagli scontri mortali a quelli con lesioni. Risultati concreti: un segnale importante e incoraggiante. Andiamo avanti con determinazione con l’obiettivo di garantire più sicurezza per tutti. E grazie, come sempre, alle Forze dell’ordine per il loro straordinario e costante impegno.</t>
+  </si>
+  <si>
+    <t>Oggi in visita alla sede della Motorizzazione Civile di Milano. Siamo impegnati per portare più personale, più mezzi, più tecnologia e per ridurre i tempi d’attesa di chi deve fare l’esame di guida, la revisione o altre pratiche. Parliamo di sicurezza: meno incidenti, meno vittime, meno feriti. Un grazie di cuore agli operatori: da Nord a Sud, stiamo investendo perché possano lavorare meglio, e perché cittadini e imprese risparmino tempo. Più sicurezza, più efficienza: è l’Italia che vogliamo.</t>
+  </si>
+  <si>
+    <t>Al via la sperimentazione delle bodycam sul personale di FS Security anche in Puglia. Nelle prossime settimane toccherà a Toscana e Piemonte, seguite dalla Lombardia tra fine maggio e inizio giugno. L’obiettivo è fare sì che entro il 2026 tutti i 1.100 operatori di FS Security vengano dotati di bodycam, da attivare in caso di pericolo. Un passo in avanti concreto per aumentare sicurezza, trasparenza e tutela di chi lavora e viaggia.</t>
+  </si>
+  <si>
+    <t>Ora in diretta da Palazzo Madama, all’evento organizzato dal Dipartimento Agricoltura della Lega: “Seminando idee, coltivando proposte, facciamo crescere l’agricoltura italiana”. State con noi!</t>
+  </si>
+  <si>
+    <t>In diretta dalla Camera dei Deputati, conferenza stampa per presentare la proposta di legge della Lega sull’occupazione giovanile. State con noi!</t>
+  </si>
+  <si>
+    <t>Il Superbollo auto è una di quelle tasse particolarmente odiose che non aiutano le casse dello Stato (perché disincentivano gli acquisti di auto potenti che in ogni caso pagherebbero più imposte) danneggiando un settore in crisi per le follie dell’Europa. Proprio per questo, oltre a volere meno tasse sulle vetture, diciamo no al Green Deal e al solo elettrico dopo il 2035. Il tutto elettrico è la morte economica, commerciale e industriale del nostro Continente.</t>
+  </si>
+  <si>
+    <t>Speriamo che le parole del Papa vengano ascoltate, e che nessuno a Bruxelles o a Parigi si metta di mezzo.</t>
+  </si>
+  <si>
+    <t>Una grande emozione, oggi, poter assistere dal vivo alla preghiera “Regina Coeli”, la prima di Papa Leone XIV. In una piazza stupenda, rumorosa, colorata, giovane, entusiasta, con tantissime ragazze e ragazzi, le parole del Santo Padre mi hanno colpito: PACE, basta guerre. Un messaggio forte, che trasmette gioia e speranza.</t>
+  </si>
+  <si>
+    <t>In diretta dalla Scuola di Formazione Politica della Lega, con l’amica Marine Le Pen ospite d’eccezione dell’ultima giornata. State con noi!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un piacere e un onore poter incontrare l’amica @MLP_officiel, che questo pomeriggio sarà ospite della Scuola di Formazione Politica della Lega.
+Combattiva, sorridente, determinata a vincere le elezioni presidenziali in Francia nel 2027 senza farsi intimidire.
+Stiamo lavorando insieme per cambiare questa Europa della burocrazia e dell’ideologia.
+Benvenuta a Roma, Marine! </t>
+  </si>
+  <si>
+    <t>Buona festa a tutte le MAMME del mondo!</t>
+  </si>
+  <si>
+    <t>Giù le mani dagli Alpini, che sono gloria, storia e patrimonio dell’Italia.</t>
+  </si>
+  <si>
+    <t>Buon viaggio sui campi di calcio Lassù al mitico Gianni Vasino, che ci ha raccontato per anni lo Sport bello e sano degli anni ‘80 e ‘90. Per voi ragazzi un volto forse poco conosciuto, per noi “anzianotti” una voce indimenticabile.</t>
+  </si>
+  <si>
+    <t>Grazie alla Lega, presto verrà ampliata la platea degli amici a quattro zampe che potranno volare accanto ai propri padroni. Una battaglia di buonsenso e di civiltà. Promessa mantenuta!</t>
+  </si>
+  <si>
+    <t>9 maggio, Giorno della memoria dedicato alle vittime del terrorismo. Mai più terrorismo, di ogni colore. Mai più violenza, di ogni colore. Mai più stragi di innocenti.</t>
+  </si>
+  <si>
+    <t>In piazza San Pietro, emozionato e commosso.
+“Pace disarmata e disarmante” ha invocato il Santo Padre, benedicendo centinaia di migliaia di fedeli.
+Buona missione Papa Leone XIV!</t>
+  </si>
+  <si>
+    <t>L’Islam, quello buono, moderato e tollerante…</t>
+  </si>
+  <si>
+    <t>Grazie a un provvedimento voluto dalla Lega, una casa occupata abusivamente è stata restituita alla proprietaria. Ottima notizia. Avanti così!</t>
+  </si>
+  <si>
+    <t>Ora in diretta dal Senato per rispondere al Question Time, state con me.</t>
+  </si>
+  <si>
+    <t>Umanità, coraggio, servizio. Grazie a chi ogni giorno sceglie di dedicare impegno, tempo e risorse per aiutare il prossimo.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dove sorgeva Expo 2015 prende vita un quartiere che guarda al futuro: gru in azione, 70.000 tra studenti, ricercatori e imprenditori pronti a vivere e innovare in uno spazio all’avanguardia. Parliamo di parchi, palestre, social housing a prezzi accessibili, residenze universitarie e tanta concretezza. Un modello vincente, portato avanti anche grazie alla Lega, che vogliamo replicare per le Olimpiadi di </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>#MilanoCortina2026</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+      </rPr>
+      <t>. Alle chiacchiere, rispondiamo con i fatti concreti. Avanti tutta!</t>
+    </r>
+  </si>
+  <si>
+    <t>Ieri hanno votato i rumeni e la comunità rumena in Italia ha dato un segnale forte: oltre il 70% ha sostenuto George Simion, il candidato vincente. Spero che nessuno osi più interferire con la democrazia in un Paese membro dell’Unione Europea. Fermare le elezioni a urne aperte e arrestare un candidato è roba da regime, non da Europa. Altro che “pericoli per la democrazia” da Le Pen o AfD… È una bella risposta a chi teme il giudizio del popolo: ha vinto la libertà. Evviva la democrazia!</t>
+  </si>
+  <si>
+    <t>164 anni di onore, coraggio e dedizione! Mentre qualcuno parla di fantomatici eserciti “europei”, noi celebriamo chi da sempre difende il nostro Paese. Viva l’Esercito ITALIANO</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GRAVISSIMO. Dopo Francia e Romania, un altro furto di Democrazia? Solidarietà ad </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>#AfD</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve"> e al popolo tedesco che, stando ai numeri, oggi li sceglierebbe come primo partito.</t>
+    </r>
+  </si>
+  <si>
+    <t>Avanti verso la Pace. E che l’Unione Europea non cerchi di far saltare il tavolo con eserciti o debiti europei per comprare nuove armi.</t>
+  </si>
+  <si>
+    <t>Due giornate belle e produttive in Trentino-Alto Adige, tra incontri con cittadini e amministratori, e sopralluoghi a cantieri, strade, ferrovie e impianti olimpici.  A Riva per la Ciclovia del Garda: l’anello ciclabile da 140 km intorno al lago sta finalmente diventando realtà. Unirà Trentino, Lombardia e Veneto, portando turismo e sviluppo.  A Trento, nei cantieri della nuova circonvallazione ferroviaria: un intervento strategico per liberare il centro.  A Baselga di Piné, per i lavori di riqualificazione dell’Ice Rink, lo stadio del ghiaccio che sarà protagonista delle Olimpiadi Invernali giovanili del 2028, grazie anche alla spinta propulsiva della Lega e delle Regioni che governiamo. Stiamo cercando di mantenere ogni impegno, uno per uno. Avanti tutta, con l’Italia del SÌ!</t>
+  </si>
+  <si>
+    <t>GRAZIE a chi lavora ogni giorno per far crescere l’Italia, a chi un lavoro dignitoso lo sta cercando, a chi il lavoro lo crea, a chi non si rassegna e non si arrende, a chi costruisce e sogna. Buon Primo Maggio a tutti!</t>
+  </si>
+  <si>
+    <t>Nella bellissima Genova, esempio di buon governo del centrodestra. Al lavoro per una città sempre più forte, moderna, efficiente e proiettata verso il futuro!</t>
+  </si>
+  <si>
+    <t>Auspico presto un incontro Trump-Zelensky-Putin per la fine della guerra. Sperando che nessuno a Bruxelles o a Parigi ostacoli la marcia verso la Pace.</t>
+  </si>
+  <si>
+    <t>In diretta dal Teatro della Gioventù di Genova per sostenere il candidato sindaco del centrodestra Pietro Piciocchi. Ci siete?</t>
+  </si>
+  <si>
+    <t>Tre giovani vite spezzate. Il mio pensiero e il mio cordoglio alle famiglie, agli amici e a tutta la comunità di Monreale. Ci dev’essere massimo impegno affinché gli assassini vengano individuati e sbattuti in galera.</t>
+  </si>
+  <si>
+    <t>Cinque anni dalla scomparsa di Pasquale Apicella, per tutti Lino, agente di Polizia ucciso a Napoli mentre era in servizio, travolto da una banda di rapinatori in fuga. Onore a Pasquale, un padre, un marito, un eroe. Oggi come allora siamo vicini alla sua splendida famiglia e a tutte le donne e gli uomini in divisa che ogni giorno rischiano la vita per difendere la nostra libertà e sicurezza. Noi non dimentichiamo.</t>
+  </si>
+  <si>
+    <t>Certa sinistra parla di libertà e di pace, poi vanno in piazza a insultare le Forze dell’ordine e con la mia immagine a testa in giù. I nostri nonni hanno lottato per lasciarci un’Italia bella e libera, non saranno sti quattro fessi a intimidirci.</t>
+  </si>
+  <si>
+    <t>Addio a Giancarlo Gentilini. Un grande sindaco, un grande alpino, un grande Veneto, un grande leghista.</t>
+  </si>
+  <si>
+    <t>Attacchi e insulti alla Polizia, falci, martelli e bandiere rosse, striscioni no-TAV e pro-Pal. Se il buongiorno si vede dal mattino, la “liberazione” che ci auguriamo è dalla violenza e dall’imbecillità.</t>
+  </si>
+  <si>
+    <t>La vera emergenza si chiama PACE, non riarmo.</t>
+  </si>
+  <si>
+    <t>Centodieci anni fa, il Genocidio armeno. Una ferita della storia. Una tragedia che costò la vita a un milione e mezzo di donne e uomini, vittime che chiedono giustizia e verità. Una memoria che non può e non deve essere dimenticata o ignorata, ma ricordata e tramandata ai nostri figli.</t>
+  </si>
+  <si>
+    <t>Dopo anni di guerra e di morte, è l’ora della Pace.</t>
+  </si>
+  <si>
+    <t>Buona Santa Pasqua di Risurrezione. Che questa giornata sia portatrice di PACE e rinnovamento, con la speranza di un futuro migliore. Auguri a tutti voi!</t>
+  </si>
+  <si>
+    <t>La Russia annuncia due giorni senza armi, è giunta l’ora di lavorare TUTTI per la pace.</t>
+  </si>
+  <si>
+    <t>Docente di Storia della Filosofia all’Università di Firenze. Sobria, obiettiva, una guida spirituale serena e profonda per i suoi studenti. Eh, ma il patriarcato…</t>
+  </si>
+  <si>
+    <t>Molto bene @GiorgiaMeloni.
+Con il governo di centrodestra l’Italia conferma di aver ritrovato prestigio internazionale e rilancio economico. Le aperture di @POTUS fanno ben sperare e vanno nella direzione auspicata da @elonmusk al congresso della Lega. Sulla fine della guerra in Ucraina, sul contrasto all’immigrazione clandestina e l’azzeramento delle politiche woke, gender e pseudo-green siamo in totale sintonia con la nuova amministrazione USA.</t>
+  </si>
+  <si>
+    <t>Oggi Banca MPS ha scritto un’altra pagina nella storia finanziaria del nostro Paese nonostante la sinistra, solo pochi anni fa, la volesse liquidare definitivamente. Gli azionisti del Monte hanno approvato i risultati per l’anno 2024, un altro bilancio straordinario che conferma tutta la fiducia che la Lega ha riposto in questo Istituto e nelle energie del suo territorio. Nella prospettiva di creare ancora più valore per l’economia del nostro Paese, gli azionisti hanno approvato con larghissimo consenso l’aumento di capitale per l’Offerta pubblica di scambio su Mediobanca. Sarà ovviamente il mercato a decidere ma conferma che la battaglia fatta per la sua esistenza dalla Lega era giusta.</t>
+  </si>
+  <si>
+    <t>Una tragedia terribile, che lascia sgomenti. Ho chiesto approfondimenti su quanto accaduto sul monte Faito, affinché si possano verificare tutti gli aspetti della vicenda e accertare eventuali responsabilità. Servono risposte rapide, chiare e inequivocabili. Ai familiari delle vittime, un pensiero e una preghiera.</t>
+  </si>
+  <si>
+    <t>Nel giorno in cui ricorre l'anniversario della sua nascita, ricordiamo Papa Benedetto XVI. Un acuto pensatore, un grande pastore, difensore delle radici cristiane dell’Europa. “Chi crede, non è mai solo”. Sempre nei nostri cuori!</t>
+  </si>
+  <si>
+    <t>Anche il Segretario generale della Nato lo dice: sostegno all'impegno del presidente americano @POTUS per la PACE. Non possiamo che essere d'accordo con questa linea. A Bruxelles, anziché continuare a parlare di bombe, missili e carri armati, qualcuno dovrebbe iniziare a prendere nota...</t>
+  </si>
+  <si>
+    <t>Più di 1.100 incidenti in meno, quasi 1.000 feriti in meno, 50 morti in meno: secondo Polizia e Carabinieri i primi quattro mesi col nuovo Codice della strada, alla faccia di fake news e polemiche lunari, confermano un trend confortante. Ringraziamo gli italiani per il senso di responsabilità e le forze dell’ordine per il consueto, straordinario, impegno. Non abbassiamo la guardia.</t>
+  </si>
+  <si>
+    <t>La Lega ha le idee chiare, noi diciamo SÌ al nucleare: pulito, sicuro, green e a emissioni zero. È l’unico modo per abbassare le bollette della luce e dell’energia per le famiglie, per l’impresa, per chi lavora.</t>
+  </si>
+  <si>
+    <t>In diretta da Milano, l’evento “Il Nucleare Sostenibile: l’Italia Riparte!” organizzato dal Dipartimento Ambiente della Lega. State con noi!</t>
+  </si>
+  <si>
+    <t>A 21 anni dalla morte, ricordiamo Fabrizio Quattrocchi, barbaramente ucciso in Iraq per mano di estremisti islamici. Un Eroe, un Grande italiano, Medaglia d’oro al Valor Civile. L’Italia non ti dimentica</t>
+  </si>
+  <si>
+    <t>Scene di violenza urbana che nulla hanno a che vedere con lo sport: questi non sono tifosi, ma delinquenti. Solidarietà agli agenti feriti.</t>
+  </si>
+  <si>
+    <t>Mentre qualcuno a Bruxelles continua a parlare di armi e guerra, la Lega lavora per la PACE. E se l’Europa vuole salvarsi, deve cambiare radicalmente. Smetta di essere onnipresente e di regolamentare tutti gli aspetti delle nostre vite, deve tornare a essere una comunità di eguali con gli stessi doveri e diritti: la Comunità Economica Europea.</t>
+  </si>
+  <si>
+    <t>Solidarietà a Giorgia per le minacce. Questi sarebbero i “pacifisti” che il 25 aprile andranno in piazza cercando fascisti che non ci sono, mentre il primo maggio parleranno di lavoro anche se non hanno mai faticato.</t>
+  </si>
+  <si>
+    <t>Mentre in Italia si avvicina l’inizio dei lavori per il Ponte sullo Stretto tra lo scetticismo di troppi media e l’ostilità della sinistra, all’estero si apprezzano gli sforzi dell’Italia del SÌ come la Napoli-Bari.</t>
+  </si>
+  <si>
+    <t>Se si fosse fermato, o meglio ancora se non avesse rubato, non gli sarebbe successo nulla. Le Forze dell’Ordine hanno fatto il loro dovere.</t>
+  </si>
+  <si>
+    <t>Un passo in avanti verso buonsenso e legalità, come da sempre proposto e sostenuto dalla Lega. Controlli sanitari, pagamento delle tasse, contrasto alla tratta e allo sfruttamento, locali dedicati, nessun giudizio morale. Che ne pensate?</t>
+  </si>
+  <si>
+    <t>Il presidente Trump “come un boss mafioso”. Così si esprime la Direttrice dell’Istituto Affari Internazionali… mi vergogno per lei.</t>
+  </si>
+  <si>
+    <t>Tanti sorrisi, strette di mano ed entusiasmo in Friuli Venezia Giulia. Tanta gente che non si arrende, che ama la propria terra e che crede in un futuro migliore. Domenica 13 e lunedì 14 aprile, dalle 7 alle 22, gli amici di Monfalcone e Pordenone hanno l’opportunità di scegliere concretezza e buonsenso, votando la Lega, con il centrodestra unito alle elezioni comunali. Avanti, futuro!</t>
+  </si>
+  <si>
+    <t>Onore alla Polizia di Stato, da 173 anni presidio di legalità, coraggio e dedizione. Dietro ogni divisa c’è una storia di impegno e amore per il Paese. A tutte le donne e gli uomini della Polizia di Stato: grazie per esserci, sempre. Gli italiani perbene sono dalla vostra parte.</t>
+  </si>
+  <si>
+    <t>Giornata di impegni in Friuli Venezia Giulia. Questa mattina a Trieste ho partecipato, insieme al presidente della Regione Massimiliano Fedriga, alla presentazione di “Agorai Innovation Hub”, centro di ricerca sull’Intelligenza Artificiale che si dedicherà all’esplorazione e allo sviluppo di soluzioni basate sull’AI in settori strategici con un focus particolare su mobilità e trasporti. Successivamente, visita al Porto di Monfalcone, un polo strategico del Nord Est per il traffico internazionale, dove sono in corso importanti interventi di modernizzazione. Innovazione, infrastrutture all’avanguardia, sviluppo. Avanti con l’Italia del SÌ!</t>
+  </si>
+  <si>
+    <t>No a guerre commerciali: chi pensa di rispondere ai dazi con contro-dazi fa il male dell'Italia, dei lavoratori e degli imprenditori italiani. Stiamo lavorando per proteggere, come Lega e governo, i confini dal punto di vista della sicurezza, ma anche per proteggere i risparmi degli italiani. Con sistemi per accompagnare le imprese esportatrici a fare sempre di più e meglio. A tutela delle eccellenze italiane, tra cui il mobile, il tessile, il vino, l'agroalimentare: dobbiamo aiutare ancora di più le aziende che esportano con l'obiettivo di difendere i risparmi degli italiani. Il governo fa tutto ciò che è in suo potere in Italia, ma è fondamentale che a Bruxelles qualcuno si svegli.</t>
+  </si>
+  <si>
+    <t>Un’Europa sana azzera domani mattina, senza ritardi, il Green Deal, il Patto di stabilità, le norme, i divieti, i vincoli, i regolamenti e tutto quello che sta soffocando le nostre imprese. È a Bruxelles il mega dazio, non altrove. È lì che bisogna usare la motosega di Milei.</t>
+  </si>
+  <si>
+    <t>Se si trovano 800 miliardi da spendere, è nostro dovere non spenderli in armi e proiettili, ma in salute, in ospedali, scuole e lavoro. Nel 2025 non esistono guerre giuste: chi sceglie la Lega, sceglie la PACE.</t>
+  </si>
+  <si>
+    <t>Un fine settimana emozionante a Firenze per il Congresso della Lega: non un partito, ma una comunità, un movimento, una grande famiglia. Andiamo avanti insieme. Viva la Lega, viva la Libertà, viva i Popoli d’Europa!</t>
+  </si>
+  <si>
+    <t>Un’altra giornata intensa, emozionante e carica di entusiasmo oggi a Firenze per la conclusione del Congresso della Lega, “Il Coraggio della Libertà”. Grazie ai tantissimi militanti accorsi da tutta Italia, agli amici e ospiti internazionali per la partecipazione e il sostegno. Nuove sfide da affrontare e una squadra più determinata che mai. Avanti insieme, con coraggio e cuore!</t>
+  </si>
+  <si>
+    <t>Vi ripropongo il mio intervento di oggi pomeriggio al Congresso della Lega a Firenze “Il Coraggio della Libertà”. Grazie, grazie e ancora grazie a tutti voi per il sostegno e la passione! La Lega non molla, mai!</t>
+  </si>
+  <si>
+    <t>Da buon militante, come da statuto, ho partecipato anche io ai voti per il congresso della Lega. Avanti a testa alta!</t>
+  </si>
+  <si>
+    <t>Cancellare le nostre radici non ci permette di accogliere chi arriva domani mattina, è un male per noi ed è un male per chi arriva. Dobbiamo essere orgogliosi di ciò che hanno fatto i nostri nonni per la nostra Patria.</t>
+  </si>
+  <si>
+    <t>Ringrazio l’amica Giorgia Meloni per il suo messaggio al congresso della Lega: l’Autonomia e il Premierato devono continuare ad andare avanti mano nella mano.</t>
+  </si>
+  <si>
+    <t>Chi sceglie la Lega fa una scelta chiara: i posti di lavoro e le case popolari, se non ci sono per tutti, vanno prima agli italiani.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -198,6 +690,10 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF000000"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -213,7 +709,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -221,6 +717,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -686,7 +1185,761 @@
         <v>49</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="A151"/>
+    <hyperlink r:id="rId2" ref="A154"/>
+  </hyperlinks>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>